--- a/data/trans_orig/P04B1_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>434091</t>
+          <t>435578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>480435</t>
+          <t>481671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>525881</t>
+          <t>527322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>585154</t>
+          <t>585019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>976499</t>
+          <t>975968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1053575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153977</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200321</t>
+          <t>198834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>140311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199449</t>
+          <t>198008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>307379</t>
+          <t>306167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383243</t>
+          <t>383774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>775113</t>
+          <t>776920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1029866</t>
+          <t>1044673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>580923</t>
+          <t>580895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>632704</t>
+          <t>633941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1379807</t>
+          <t>1373128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1699627</t>
+          <t>1689842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160872</t>
+          <t>146065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415625</t>
+          <t>413818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321273</t>
+          <t>320036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373054</t>
+          <t>373082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445088</t>
+          <t>454873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>764908</t>
+          <t>771587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>524945</t>
+          <t>523415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>572348</t>
+          <t>572620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>674058</t>
+          <t>674297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>828683</t>
+          <t>842483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1223738</t>
+          <t>1223257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1408620</t>
+          <t>1395518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131236</t>
+          <t>130964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178639</t>
+          <t>180169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258652</t>
+          <t>258413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227674</t>
+          <t>240776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412556</t>
+          <t>413037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>560536</t>
+          <t>556599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>621585</t>
+          <t>617996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>653592</t>
+          <t>651326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>774398</t>
+          <t>772863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1227369</t>
+          <t>1228712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1367194</t>
+          <t>1363081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304215</t>
+          <t>307804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365264</t>
+          <t>369201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318520</t>
+          <t>320055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>439326</t>
+          <t>441592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651524</t>
+          <t>655637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>791349</t>
+          <t>790006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2369539</t>
+          <t>2372691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2678590</t>
+          <t>2678784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2497834</t>
+          <t>2488685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2806501</t>
+          <t>2800898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4908917</t>
+          <t>4909939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5325501</t>
+          <t>5309435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>775944</t>
+          <t>775750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1084995</t>
+          <t>1081843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>898434</t>
+          <t>904037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1207101</t>
+          <t>1216250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1833968</t>
+          <t>1850034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2250552</t>
+          <t>2249530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>457717</t>
+          <t>487901</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>435578</t>
+          <t>461627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>481671</t>
+          <t>513137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>549909</t>
+          <t>535315</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>527322</t>
+          <t>513247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>585019</t>
+          <t>554276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1007626</t>
+          <t>1023217</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>993215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1053575</t>
+          <t>1057389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>176695</t>
+          <t>201727</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>176491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198834</t>
+          <t>228001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>175421</t>
+          <t>198865</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140311</t>
+          <t>179904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198008</t>
+          <t>220933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>352116</t>
+          <t>400591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306167</t>
+          <t>366419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383774</t>
+          <t>430593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1359742</t>
+          <t>1423808</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1359742</t>
+          <t>1423808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1359742</t>
+          <t>1423808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>872223</t>
+          <t>671982</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>776920</t>
+          <t>634050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1044673</t>
+          <t>703779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607503</t>
+          <t>671733</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>580895</t>
+          <t>643077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>633941</t>
+          <t>699941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1479726</t>
+          <t>1343715</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1373128</t>
+          <t>1296648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1689842</t>
+          <t>1388394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>318515</t>
+          <t>374470</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146065</t>
+          <t>342673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413818</t>
+          <t>412402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>346474</t>
+          <t>393460</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320036</t>
+          <t>365252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373082</t>
+          <t>422116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>664989</t>
+          <t>767930</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454873</t>
+          <t>723251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771587</t>
+          <t>814997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190738</t>
+          <t>1046452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190738</t>
+          <t>1046452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190738</t>
+          <t>1046452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>953977</t>
+          <t>1065193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>953977</t>
+          <t>1065193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>953977</t>
+          <t>1065193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2144715</t>
+          <t>2111645</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2144715</t>
+          <t>2111645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2144715</t>
+          <t>2111645</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>547496</t>
+          <t>622427</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>523415</t>
+          <t>595603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>572620</t>
+          <t>650110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>740689</t>
+          <t>582925</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>674297</t>
+          <t>558356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>842483</t>
+          <t>606895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1288185</t>
+          <t>1205353</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1223257</t>
+          <t>1168583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1395518</t>
+          <t>1241542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156088</t>
+          <t>178464</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130964</t>
+          <t>150781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180169</t>
+          <t>205288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>192021</t>
+          <t>228627</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90227</t>
+          <t>204657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258413</t>
+          <t>253196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>348109</t>
+          <t>407090</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>370901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>413037</t>
+          <t>443860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703584</t>
+          <t>800891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703584</t>
+          <t>800891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703584</t>
+          <t>800891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636294</t>
+          <t>1612443</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636294</t>
+          <t>1612443</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636294</t>
+          <t>1612443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>590624</t>
+          <t>600782</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>556599</t>
+          <t>568302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>617996</t>
+          <t>635255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>691605</t>
+          <t>649075</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>651326</t>
+          <t>619383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>772863</t>
+          <t>679939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1282229</t>
+          <t>1249856</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1228712</t>
+          <t>1205126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1363081</t>
+          <t>1297061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>335176</t>
+          <t>386800</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307804</t>
+          <t>352327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369201</t>
+          <t>419280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>401313</t>
+          <t>467868</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320055</t>
+          <t>437004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441592</t>
+          <t>497560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>736489</t>
+          <t>854668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655637</t>
+          <t>807463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>790006</t>
+          <t>899398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925800</t>
+          <t>987582</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925800</t>
+          <t>987582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925800</t>
+          <t>987582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092918</t>
+          <t>1116943</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092918</t>
+          <t>1116943</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092918</t>
+          <t>1116943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018718</t>
+          <t>2104524</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018718</t>
+          <t>2104524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018718</t>
+          <t>2104524</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2468061</t>
+          <t>2383093</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2372691</t>
+          <t>2327305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2678784</t>
+          <t>2444983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2589706</t>
+          <t>2439047</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2488685</t>
+          <t>2385894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2800898</t>
+          <t>2493646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5057767</t>
+          <t>4822141</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4909939</t>
+          <t>4744488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5309435</t>
+          <t>4899166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>986473</t>
+          <t>1141460</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>775750</t>
+          <t>1079570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1081843</t>
+          <t>1197248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1115229</t>
+          <t>1288820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>904037</t>
+          <t>1234221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1216250</t>
+          <t>1341973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2101702</t>
+          <t>2430279</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1850034</t>
+          <t>2353254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2249530</t>
+          <t>2507932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
